--- a/UI Iterative Design.xlsx
+++ b/UI Iterative Design.xlsx
@@ -70,13 +70,13 @@
     <t xml:space="preserve">Collidable</t>
   </si>
   <si>
+    <t xml:space="preserve">UI String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI Int</t>
+  </si>
+  <si>
     <t xml:space="preserve">UI Float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI Int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI String</t>
   </si>
   <si>
     <t xml:space="preserve">UI Container</t>
@@ -94,6 +94,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -115,6 +116,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -178,40 +180,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -224,23 +230,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4DFB32"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -418,207 +407,207 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="8.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="11.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="12.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="8.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="11.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="0"/>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="0"/>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="0"/>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="0"/>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="0"/>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="0"/>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="0"/>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="0"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="0"/>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="C11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="C12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>6</v>
       </c>
     </row>
